--- a/data/trans_orig/P36BPD04_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD04_2023-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de consumo de fruta o zumos naturales en 2023</t>
+          <t>Población según la frecuencia de consumo de fruta o zumos naturales en 2023 (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10176</t>
+          <t>10016</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28427</t>
+          <t>28317</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11180</t>
+          <t>11082</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>36816</t>
+          <t>36721</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>24552</t>
+          <t>24702</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>53125</t>
+          <t>54562</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>9,08%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>121321</t>
+          <t>119829</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>163841</t>
+          <t>163589</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>38,95%</t>
+          <t>38,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>52,61%</t>
+          <t>52,53%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>127850</t>
+          <t>127463</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>155191</t>
+          <t>156027</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>44,14%</t>
+          <t>44,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>53,58%</t>
+          <t>53,87%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>258633</t>
+          <t>253617</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>311767</t>
+          <t>308968</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>43,03%</t>
+          <t>42,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>51,87%</t>
+          <t>51,4%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>116841</t>
+          <t>115524</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>159794</t>
+          <t>158873</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>37,52%</t>
+          <t>37,09%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>51,31%</t>
+          <t>51,01%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>100189</t>
+          <t>99909</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>126520</t>
+          <t>126518</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>34,49%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>225617</t>
+          <t>228436</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>277167</t>
+          <t>281022</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>37,54%</t>
+          <t>38,0%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>46,11%</t>
+          <t>46,75%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8953</t>
+          <t>8684</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23684</t>
+          <t>23974</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10853</t>
+          <t>10224</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21422</t>
+          <t>21497</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>23495</t>
+          <t>22781</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>41377</t>
+          <t>40854</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,8%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>32276</t>
+          <t>33343</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>68597</t>
+          <t>69022</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18603</t>
+          <t>19021</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>36758</t>
+          <t>37803</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>57478</t>
+          <t>56708</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>95141</t>
+          <t>98003</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,48%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>102353</t>
+          <t>102514</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>154357</t>
+          <t>152400</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>90762</t>
+          <t>91625</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>124180</t>
+          <t>125584</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>202613</t>
+          <t>204202</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>264234</t>
+          <t>264969</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>25,64%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>289240</t>
+          <t>289536</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>348659</t>
+          <t>349622</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>55,8%</t>
+          <t>55,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>67,26%</t>
+          <t>67,44%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>333056</t>
+          <t>333902</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>371573</t>
+          <t>372242</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>64,68%</t>
+          <t>64,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>72,15%</t>
+          <t>72,28%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>638149</t>
+          <t>634548</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>704928</t>
+          <t>706981</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>61,75%</t>
+          <t>61,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>68,22%</t>
+          <t>68,42%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>15263</t>
+          <t>14727</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>37685</t>
+          <t>37225</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>20640</t>
+          <t>20631</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>39525</t>
+          <t>39171</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>39860</t>
+          <t>39744</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>68032</t>
+          <t>69328</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,71%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>16056</t>
+          <t>16942</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>36101</t>
+          <t>36877</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>12613</t>
+          <t>12743</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>28351</t>
+          <t>27335</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>33207</t>
+          <t>32274</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>57787</t>
+          <t>57165</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,63%</t>
         </is>
       </c>
     </row>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>86307</t>
+          <t>84830</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>31288</t>
+          <t>32434</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>53520</t>
+          <t>54554</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>93129</t>
+          <t>93106</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>131793</t>
+          <t>130773</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>19,75%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>138211</t>
+          <t>139149</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>172020</t>
+          <t>172833</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>43,73%</t>
+          <t>44,03%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>54,43%</t>
+          <t>54,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>172392</t>
+          <t>173822</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>203960</t>
+          <t>205866</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>49,82%</t>
+          <t>50,23%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>58,94%</t>
+          <t>59,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>321566</t>
+          <t>321316</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>369072</t>
+          <t>369854</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>48,57%</t>
+          <t>48,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>55,74%</t>
+          <t>55,86%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>51998</t>
+          <t>53277</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>78637</t>
+          <t>81335</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>81634</t>
+          <t>81499</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>110071</t>
+          <t>110900</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>32,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>141125</t>
+          <t>142768</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>180637</t>
+          <t>182237</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>27,53%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>2643</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21620</t>
+          <t>21508</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5872</t>
+          <t>6231</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>21862</t>
+          <t>21642</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>11629</t>
+          <t>11261</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>33122</t>
+          <t>32454</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,12%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>22918</t>
+          <t>21894</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>51297</t>
+          <t>50330</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>20818</t>
+          <t>21716</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>54342</t>
+          <t>53670</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>50536</t>
+          <t>50251</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>93790</t>
+          <t>93456</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,86%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>114873</t>
+          <t>119617</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>159520</t>
+          <t>160704</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>38,27%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>51,04%</t>
+          <t>51,42%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>198830</t>
+          <t>203685</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>332850</t>
+          <t>340119</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>41,8%</t>
+          <t>42,82%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>69,97%</t>
+          <t>71,5%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>334823</t>
+          <t>337900</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>501033</t>
+          <t>498647</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>42,48%</t>
+          <t>42,87%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>63,56%</t>
+          <t>63,26%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>112445</t>
+          <t>112410</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>159353</t>
+          <t>157219</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>35,96%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>50,98%</t>
+          <t>50,3%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>110480</t>
+          <t>108210</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>228247</t>
+          <t>228934</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>47,98%</t>
+          <t>48,12%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>225916</t>
+          <t>228855</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>365273</t>
+          <t>364826</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>46,34%</t>
+          <t>46,28%</t>
         </is>
       </c>
     </row>
@@ -3011,7 +3011,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>5461</t>
+          <t>5529</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3026,7 +3026,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>515</t>
+          <t>509</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4118</t>
+          <t>4091</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1251</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6966</t>
+          <t>7372</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,9%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5084</t>
+          <t>4931</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>16760</t>
+          <t>16581</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1668</t>
+          <t>1890</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>9508</t>
+          <t>10103</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>8050</t>
+          <t>8145</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>22004</t>
+          <t>22277</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,76%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>105523</t>
+          <t>105442</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>126684</t>
+          <t>126524</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>59,04%</t>
+          <t>58,99%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>70,88%</t>
+          <t>70,79%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>114587</t>
+          <t>115242</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>134320</t>
+          <t>134161</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>55,02%</t>
+          <t>55,33%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>64,49%</t>
+          <t>64,42%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>225650</t>
+          <t>225730</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>253772</t>
+          <t>256296</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>58,31%</t>
+          <t>58,33%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>65,57%</t>
+          <t>66,22%</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>41734</t>
+          <t>41801</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>61872</t>
+          <t>62011</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>34,69%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>68410</t>
+          <t>68054</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>87604</t>
+          <t>86797</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>42,06%</t>
+          <t>41,67%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>116065</t>
+          <t>114989</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>143325</t>
+          <t>143727</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>37,03%</t>
+          <t>37,14%</t>
         </is>
       </c>
     </row>
@@ -3575,12 +3575,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>4372</t>
+          <t>4631</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>16987</t>
+          <t>17307</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3590,12 +3590,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>4916</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>15631</t>
+          <t>16395</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3645,12 +3645,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>11134</t>
+          <t>10737</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>28292</t>
+          <t>28171</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,35%</t>
         </is>
       </c>
     </row>
@@ -3688,12 +3688,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>53554</t>
+          <t>52779</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>81590</t>
+          <t>79853</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3703,12 +3703,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>29,62%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>40170</t>
+          <t>39410</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>62868</t>
+          <t>64025</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3738,12 +3738,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>100922</t>
+          <t>101899</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>136802</t>
+          <t>135968</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3773,12 +3773,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>25,82%</t>
         </is>
       </c>
     </row>
@@ -3801,12 +3801,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>146517</t>
+          <t>149129</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>175117</t>
+          <t>176857</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>54,34%</t>
+          <t>55,31%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>64,95%</t>
+          <t>65,59%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>150645</t>
+          <t>151449</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>176103</t>
+          <t>176672</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3851,12 +3851,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>58,6%</t>
+          <t>58,92%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>68,51%</t>
+          <t>68,73%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>305029</t>
+          <t>307896</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>345241</t>
+          <t>346733</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3886,12 +3886,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>57,91%</t>
+          <t>58,46%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>65,55%</t>
+          <t>65,83%</t>
         </is>
       </c>
     </row>
@@ -3914,12 +3914,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>23870</t>
+          <t>24521</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>41068</t>
+          <t>40897</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3929,12 +3929,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3949,12 +3949,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>24897</t>
+          <t>25551</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>41539</t>
+          <t>41071</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3964,12 +3964,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3984,12 +3984,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>54558</t>
+          <t>54137</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>75695</t>
+          <t>75512</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3999,12 +3999,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,34%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>55764</t>
+          <t>56211</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>106759</t>
+          <t>105414</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>97377</t>
+          <t>95898</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>530600</t>
+          <t>564507</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>62,48%</t>
+          <t>66,47%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>168972</t>
+          <t>169380</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>804457</t>
+          <t>767320</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>54,64%</t>
+          <t>52,12%</t>
         </is>
       </c>
     </row>
@@ -4257,12 +4257,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>71172</t>
+          <t>69481</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>117019</t>
+          <t>114880</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>45128</t>
+          <t>44858</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>122555</t>
+          <t>124892</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>114530</t>
+          <t>114152</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>222424</t>
+          <t>223211</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,16%</t>
         </is>
       </c>
     </row>
@@ -4370,12 +4370,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>218126</t>
+          <t>217263</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>277225</t>
+          <t>274514</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4385,12 +4385,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>34,87%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>44,49%</t>
+          <t>44,06%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>150282</t>
+          <t>136949</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>364284</t>
+          <t>366079</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>42,89%</t>
+          <t>43,11%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>323146</t>
+          <t>321234</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>612858</t>
+          <t>611511</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>41,62%</t>
+          <t>41,53%</t>
         </is>
       </c>
     </row>
@@ -4483,12 +4483,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>179317</t>
+          <t>180225</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>235740</t>
+          <t>235267</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>37,83%</t>
+          <t>37,76%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4518,12 +4518,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>111397</t>
+          <t>102556</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>282695</t>
+          <t>280476</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4533,12 +4533,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>33,03%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4553,12 +4553,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>240306</t>
+          <t>257775</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>498751</t>
+          <t>494776</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>33,6%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>7455</t>
+          <t>7577</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>32437</t>
+          <t>33058</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>9903</t>
+          <t>9535</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>22889</t>
+          <t>22783</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>21216</t>
+          <t>20008</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>50168</t>
+          <t>50008</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>27587</t>
+          <t>33740</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>102763</t>
+          <t>103410</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>45896</t>
+          <t>46733</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>70806</t>
+          <t>71188</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>79983</t>
+          <t>73625</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>159471</t>
+          <t>160059</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,72%</t>
         </is>
       </c>
     </row>
@@ -4939,12 +4939,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>668119</t>
+          <t>667737</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>850825</t>
+          <t>845705</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4954,12 +4954,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>71,94%</t>
+          <t>71,9%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>91,06%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4974,12 +4974,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>530941</t>
+          <t>528945</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>570627</t>
+          <t>571536</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>73,97%</t>
+          <t>73,7%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>79,5%</t>
+          <t>79,63%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1220245</t>
+          <t>1217389</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>1428630</t>
+          <t>1424586</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>74,11%</t>
+          <t>73,94%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>86,77%</t>
+          <t>86,52%</t>
         </is>
       </c>
     </row>
@@ -5052,12 +5052,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>42164</t>
+          <t>40705</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>136632</t>
+          <t>138838</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5067,12 +5067,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>79228</t>
+          <t>76761</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>113620</t>
+          <t>112167</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5102,12 +5102,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>113807</t>
+          <t>120564</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>232121</t>
+          <t>234025</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5137,12 +5137,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>14,21%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>160937</t>
+          <t>158122</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>254177</t>
+          <t>247224</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>180996</t>
+          <t>181595</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>993277</t>
+          <t>1118414</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>383053</t>
+          <t>379476</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>1295234</t>
+          <t>1380234</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>19,39%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>472190</t>
+          <t>467138</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>682254</t>
+          <t>674007</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>431420</t>
+          <t>435251</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>581725</t>
+          <t>583919</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>975893</t>
+          <t>974631</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>1230057</t>
+          <t>1244859</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,49%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>1877395</t>
+          <t>1894690</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>2302735</t>
+          <t>2369611</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>54,28%</t>
+          <t>54,78%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>66,58%</t>
+          <t>68,51%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>1653151</t>
+          <t>1615310</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>2176957</t>
+          <t>2174129</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>45,18%</t>
+          <t>44,15%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>59,5%</t>
+          <t>59,42%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>3720029</t>
+          <t>3688216</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>4317148</t>
+          <t>4347843</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>52,27%</t>
+          <t>51,82%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>60,66%</t>
+          <t>61,09%</t>
         </is>
       </c>
     </row>
@@ -5621,12 +5621,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>484201</t>
+          <t>489481</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>696220</t>
+          <t>694271</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5636,12 +5636,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>594530</t>
+          <t>607721</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>812627</t>
+          <t>812179</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>1177004</t>
+          <t>1157964</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>1466550</t>
+          <t>1480467</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>20,8%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P36BPD04_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD04_2023-Provincia-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>17196</t>
+          <t>17312</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10016</t>
+          <t>10341</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28317</t>
+          <t>27127</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>18667</t>
+          <t>16880</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11082</t>
+          <t>10300</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>36721</t>
+          <t>27658</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>35863</t>
+          <t>34192</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>24702</t>
+          <t>24811</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>54562</t>
+          <t>48216</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>7,59%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>141257</t>
+          <t>134998</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>119829</t>
+          <t>116414</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>163589</t>
+          <t>155332</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>45,36%</t>
+          <t>42,34%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>38,48%</t>
+          <t>36,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>52,53%</t>
+          <t>48,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>141891</t>
+          <t>145080</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>127463</t>
+          <t>129100</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>156027</t>
+          <t>159293</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>48,99%</t>
+          <t>45,9%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>44,01%</t>
+          <t>40,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>53,87%</t>
+          <t>50,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>283147</t>
+          <t>280079</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>253617</t>
+          <t>255809</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>308968</t>
+          <t>302532</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>47,11%</t>
+          <t>44,11%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>42,19%</t>
+          <t>40,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>51,4%</t>
+          <t>47,65%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>137715</t>
+          <t>149700</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>115524</t>
+          <t>128661</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>158873</t>
+          <t>167541</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>44,22%</t>
+          <t>46,95%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>40,35%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>51,01%</t>
+          <t>52,55%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>113481</t>
+          <t>136520</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>99909</t>
+          <t>121991</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>126518</t>
+          <t>151682</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>39,18%</t>
+          <t>43,19%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>38,6%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>43,68%</t>
+          <t>47,99%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>251196</t>
+          <t>286220</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>228436</t>
+          <t>262985</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>281022</t>
+          <t>310825</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>41,79%</t>
+          <t>45,08%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>38,0%</t>
+          <t>41,42%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>46,75%</t>
+          <t>48,96%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>15275</t>
+          <t>16835</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8684</t>
+          <t>10441</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23974</t>
+          <t>26390</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>15596</t>
+          <t>17580</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10224</t>
+          <t>12826</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21497</t>
+          <t>24449</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>30871</t>
+          <t>34415</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>22781</t>
+          <t>25617</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>40854</t>
+          <t>45042</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>7,09%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>47509</t>
+          <t>48774</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>33343</t>
+          <t>34231</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>69022</t>
+          <t>67787</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>26419</t>
+          <t>28154</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>19021</t>
+          <t>20317</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>37803</t>
+          <t>38876</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>73928</t>
+          <t>76928</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>56708</t>
+          <t>58889</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>98003</t>
+          <t>98873</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,18%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>125760</t>
+          <t>128833</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>102514</t>
+          <t>104769</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>152400</t>
+          <t>151897</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>107391</t>
+          <t>113484</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>91625</t>
+          <t>96175</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>125584</t>
+          <t>131026</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>233150</t>
+          <t>242317</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>204202</t>
+          <t>215085</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>264969</t>
+          <t>272356</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>25,29%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>320868</t>
+          <t>327009</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>289536</t>
+          <t>300483</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>349622</t>
+          <t>353818</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>61,9%</t>
+          <t>61,62%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>55,85%</t>
+          <t>56,63%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>67,44%</t>
+          <t>66,68%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>352574</t>
+          <t>375704</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>333902</t>
+          <t>356874</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>372242</t>
+          <t>393854</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>68,47%</t>
+          <t>68,75%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>64,84%</t>
+          <t>65,3%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>72,28%</t>
+          <t>72,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>673442</t>
+          <t>702713</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>634548</t>
+          <t>666340</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>706981</t>
+          <t>733888</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>65,17%</t>
+          <t>65,24%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>61,41%</t>
+          <t>61,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>68,42%</t>
+          <t>68,13%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>24254</t>
+          <t>26031</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>14727</t>
+          <t>17373</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>37225</t>
+          <t>38690</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>28586</t>
+          <t>29152</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>20631</t>
+          <t>20613</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>39171</t>
+          <t>40517</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>52840</t>
+          <t>55183</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>39744</t>
+          <t>39634</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>69328</t>
+          <t>70631</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,56%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>25255</t>
+          <t>25541</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>16942</t>
+          <t>17064</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>36877</t>
+          <t>37525</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>19042</t>
+          <t>19376</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>12743</t>
+          <t>12869</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>27335</t>
+          <t>28382</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>44298</t>
+          <t>44917</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>32274</t>
+          <t>34083</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>57165</t>
+          <t>58912</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,8%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>69618</t>
+          <t>68867</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>55757</t>
+          <t>54333</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>84830</t>
+          <t>84347</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>41573</t>
+          <t>43081</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>32434</t>
+          <t>32977</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>54554</t>
+          <t>55524</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>111192</t>
+          <t>111948</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>93106</t>
+          <t>95034</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>130773</t>
+          <t>132357</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,78%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>155989</t>
+          <t>156960</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>139149</t>
+          <t>138427</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>172833</t>
+          <t>173026</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>49,36%</t>
+          <t>49,67%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>44,03%</t>
+          <t>43,81%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>54,69%</t>
+          <t>54,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>189583</t>
+          <t>195391</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>173822</t>
+          <t>181544</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>205866</t>
+          <t>212207</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>54,79%</t>
+          <t>55,32%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>50,23%</t>
+          <t>51,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>59,49%</t>
+          <t>60,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>345572</t>
+          <t>352351</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>321316</t>
+          <t>327982</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>369854</t>
+          <t>374736</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>52,2%</t>
+          <t>52,65%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>48,53%</t>
+          <t>49,01%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>55,86%</t>
+          <t>56,0%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>65187</t>
+          <t>64626</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>53277</t>
+          <t>52354</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>81335</t>
+          <t>79342</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>25,11%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>95827</t>
+          <t>95351</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>81499</t>
+          <t>81580</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>110900</t>
+          <t>108732</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>32,05%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>161014</t>
+          <t>159976</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>142768</t>
+          <t>142843</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>182237</t>
+          <t>181065</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>27,06%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>346025</t>
+          <t>353199</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>346025</t>
+          <t>353199</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>346025</t>
+          <t>353199</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>662076</t>
+          <t>669192</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>662076</t>
+          <t>669192</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>662076</t>
+          <t>669192</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>7626</t>
+          <t>8241</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2643</t>
+          <t>2496</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21508</t>
+          <t>22132</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>12209</t>
+          <t>12875</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6231</t>
+          <t>7566</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>21642</t>
+          <t>22130</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>19836</t>
+          <t>21117</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>11261</t>
+          <t>12557</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>32454</t>
+          <t>36040</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,53%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>33673</t>
+          <t>36532</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>21894</t>
+          <t>24840</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>50330</t>
+          <t>55336</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>38040</t>
+          <t>43656</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>21716</t>
+          <t>32284</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>53670</t>
+          <t>58420</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>71713</t>
+          <t>80188</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>50251</t>
+          <t>63232</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>93456</t>
+          <t>102124</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>12,84%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>138907</t>
+          <t>158829</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>119617</t>
+          <t>133619</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>160704</t>
+          <t>181916</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>44,44%</t>
+          <t>42,56%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>38,27%</t>
+          <t>35,81%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>51,42%</t>
+          <t>48,75%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>254047</t>
+          <t>206134</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>203685</t>
+          <t>186224</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>340119</t>
+          <t>224952</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>53,4%</t>
+          <t>48,85%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>42,82%</t>
+          <t>44,13%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>71,5%</t>
+          <t>53,31%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>392954</t>
+          <t>364963</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>337900</t>
+          <t>333450</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>498647</t>
+          <t>398014</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>49,85%</t>
+          <t>45,9%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>42,87%</t>
+          <t>41,94%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>63,26%</t>
+          <t>50,06%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>132350</t>
+          <t>169543</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>112410</t>
+          <t>142611</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>157219</t>
+          <t>194273</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>42,34%</t>
+          <t>45,44%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>35,96%</t>
+          <t>38,22%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>50,3%</t>
+          <t>52,06%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>171421</t>
+          <t>159296</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>108210</t>
+          <t>141185</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>228934</t>
+          <t>180132</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>36,03%</t>
+          <t>37,75%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>33,46%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>48,12%</t>
+          <t>42,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>303771</t>
+          <t>328839</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>228855</t>
+          <t>296718</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>364826</t>
+          <t>359594</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>41,36%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>37,32%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>46,28%</t>
+          <t>45,23%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3001,7 +3001,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1448</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -3011,12 +3011,12 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>5529</t>
+          <t>5345</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -3026,7 +3026,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,32 +3036,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1822</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>509</t>
+          <t>395</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4091</t>
+          <t>5345</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,17 +3071,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>3270</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1291</t>
+          <t>1495</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>7372</t>
+          <t>8298</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>9437</t>
+          <t>10950</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4931</t>
+          <t>6107</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>16581</t>
+          <t>19223</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,17 +3149,17 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>4275</t>
+          <t>4647</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1890</t>
+          <t>1957</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>10103</t>
+          <t>12156</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>13711</t>
+          <t>15597</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>8145</t>
+          <t>9449</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>22277</t>
+          <t>24743</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,72%</t>
         </is>
       </c>
     </row>
@@ -3227,32 +3227,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>116256</t>
+          <t>132335</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>105442</t>
+          <t>118569</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>126524</t>
+          <t>144198</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>65,04%</t>
+          <t>64,34%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>58,99%</t>
+          <t>57,65%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>70,79%</t>
+          <t>70,11%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,32 +3262,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>124634</t>
+          <t>134803</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>115242</t>
+          <t>123783</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>134161</t>
+          <t>145104</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>59,84%</t>
+          <t>59,43%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>55,33%</t>
+          <t>54,57%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>64,42%</t>
+          <t>63,97%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>240890</t>
+          <t>267137</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>225730</t>
+          <t>248451</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>256296</t>
+          <t>283440</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>62,24%</t>
+          <t>61,77%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>58,33%</t>
+          <t>57,45%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>66,22%</t>
+          <t>65,54%</t>
         </is>
       </c>
     </row>
@@ -3340,32 +3340,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>51602</t>
+          <t>60729</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>41801</t>
+          <t>49657</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>62011</t>
+          <t>72960</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>29,53%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>34,69%</t>
+          <t>35,48%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3375,32 +3375,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>77544</t>
+          <t>85371</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>68054</t>
+          <t>74796</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>86797</t>
+          <t>96249</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>37,23%</t>
+          <t>37,64%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>32,98%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>41,67%</t>
+          <t>42,43%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>129145</t>
+          <t>146100</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>114989</t>
+          <t>128974</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>143727</t>
+          <t>162412</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>33,78%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>29,82%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>37,14%</t>
+          <t>37,55%</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3570,32 +3570,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>9370</t>
+          <t>8932</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>4631</t>
+          <t>3983</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>17307</t>
+          <t>16291</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3605,32 +3605,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>8679</t>
+          <t>8625</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>4916</t>
+          <t>4266</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>16395</t>
+          <t>15144</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,32 +3640,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>18049</t>
+          <t>17557</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>10737</t>
+          <t>10798</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>28171</t>
+          <t>26726</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,0%</t>
         </is>
       </c>
     </row>
@@ -3683,32 +3683,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>66509</t>
+          <t>67573</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>52779</t>
+          <t>55918</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>79853</t>
+          <t>82815</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3718,32 +3718,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>51293</t>
+          <t>52929</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>39410</t>
+          <t>42075</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>64025</t>
+          <t>65871</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,32 +3753,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>117801</t>
+          <t>120502</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>101899</t>
+          <t>104106</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>135968</t>
+          <t>140476</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>26,28%</t>
         </is>
       </c>
     </row>
@@ -3796,32 +3796,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>162204</t>
+          <t>162378</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>149129</t>
+          <t>147194</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>176857</t>
+          <t>175956</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>60,16%</t>
+          <t>59,98%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>55,31%</t>
+          <t>54,37%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>65,59%</t>
+          <t>65,0%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3831,32 +3831,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>164573</t>
+          <t>168586</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>151449</t>
+          <t>155773</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>176672</t>
+          <t>180931</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>64,02%</t>
+          <t>63,92%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>58,92%</t>
+          <t>59,06%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>68,73%</t>
+          <t>68,6%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3866,32 +3866,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>326778</t>
+          <t>330964</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>307896</t>
+          <t>310798</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>346733</t>
+          <t>347874</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>62,04%</t>
+          <t>61,93%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>58,46%</t>
+          <t>58,15%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>65,83%</t>
+          <t>65,09%</t>
         </is>
       </c>
     </row>
@@ -3909,32 +3909,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>31553</t>
+          <t>31824</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>24521</t>
+          <t>24402</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>40897</t>
+          <t>41362</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3944,32 +3944,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>32511</t>
+          <t>33610</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>25551</t>
+          <t>26130</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>41071</t>
+          <t>41850</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3979,32 +3979,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>64064</t>
+          <t>65434</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>54137</t>
+          <t>55075</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>75512</t>
+          <t>78128</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,62%</t>
         </is>
       </c>
     </row>
@@ -4022,17 +4022,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4057,17 +4057,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4092,17 +4092,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4139,32 +4139,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>76605</t>
+          <t>78252</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>56211</t>
+          <t>60149</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>105414</t>
+          <t>101741</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4174,32 +4174,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>283793</t>
+          <t>93969</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>95898</t>
+          <t>77871</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>564507</t>
+          <t>115679</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>33,42%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>66,47%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4209,32 +4209,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>360398</t>
+          <t>172220</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>169380</t>
+          <t>145011</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>767320</t>
+          <t>200945</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>52,12%</t>
+          <t>13,49%</t>
         </is>
       </c>
     </row>
@@ -4252,32 +4252,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>92073</t>
+          <t>108092</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>69481</t>
+          <t>87555</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>114880</t>
+          <t>133759</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4287,32 +4287,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>88030</t>
+          <t>102551</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>44858</t>
+          <t>85009</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>124892</t>
+          <t>126845</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4322,32 +4322,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>180103</t>
+          <t>210643</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>114152</t>
+          <t>180460</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>223211</t>
+          <t>243005</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>16,31%</t>
         </is>
       </c>
     </row>
@@ -4365,32 +4365,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>246808</t>
+          <t>283540</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>217263</t>
+          <t>254147</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>274514</t>
+          <t>317066</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>39,61%</t>
+          <t>39,52%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>34,87%</t>
+          <t>35,42%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>44,06%</t>
+          <t>44,19%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4400,32 +4400,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>270488</t>
+          <t>325081</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>136949</t>
+          <t>299314</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>366079</t>
+          <t>350122</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>42,11%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>38,77%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>43,11%</t>
+          <t>45,35%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4435,32 +4435,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>517296</t>
+          <t>608621</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>321234</t>
+          <t>570307</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>611511</t>
+          <t>645873</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>35,13%</t>
+          <t>40,86%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>38,29%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>41,53%</t>
+          <t>43,36%</t>
         </is>
       </c>
     </row>
@@ -4478,32 +4478,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>207599</t>
+          <t>247604</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>180225</t>
+          <t>219494</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>235267</t>
+          <t>277605</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>34,51%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>37,76%</t>
+          <t>38,69%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4513,32 +4513,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>206955</t>
+          <t>250456</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>102556</t>
+          <t>227586</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>280476</t>
+          <t>275042</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>32,44%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>35,62%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4548,32 +4548,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>414554</t>
+          <t>498060</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>257775</t>
+          <t>462794</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>494776</t>
+          <t>536221</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>33,44%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>33,6%</t>
+          <t>36,0%</t>
         </is>
       </c>
     </row>
@@ -4591,17 +4591,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>623086</t>
+          <t>717487</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>623086</t>
+          <t>717487</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>623086</t>
+          <t>717487</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4626,17 +4626,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4661,17 +4661,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>1472351</t>
+          <t>1489544</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1472351</t>
+          <t>1489544</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1472351</t>
+          <t>1489544</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4708,32 +4708,32 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>19361</t>
+          <t>21538</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>7577</t>
+          <t>12566</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>33058</t>
+          <t>32472</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4743,32 +4743,32 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>15377</t>
+          <t>19157</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>9535</t>
+          <t>12216</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>22783</t>
+          <t>28594</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4778,32 +4778,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>34738</t>
+          <t>40695</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>20008</t>
+          <t>29043</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>50008</t>
+          <t>54550</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,35%</t>
         </is>
       </c>
     </row>
@@ -4821,32 +4821,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>70243</t>
+          <t>81802</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>33740</t>
+          <t>64971</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>103410</t>
+          <t>100364</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4856,32 +4856,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>58073</t>
+          <t>68415</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>46733</t>
+          <t>55453</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>71188</t>
+          <t>85926</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4891,32 +4891,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>128317</t>
+          <t>150217</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>73625</t>
+          <t>126652</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>160059</t>
+          <t>175765</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>10,79%</t>
         </is>
       </c>
     </row>
@@ -4934,32 +4934,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>743097</t>
+          <t>584202</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>667737</t>
+          <t>558467</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>845705</t>
+          <t>609456</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>80,01%</t>
+          <t>73,2%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>71,9%</t>
+          <t>69,98%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>76,37%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4969,32 +4969,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>551583</t>
+          <t>642298</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>528945</t>
+          <t>617797</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>571536</t>
+          <t>663737</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>76,85%</t>
+          <t>77,26%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>73,7%</t>
+          <t>74,31%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>79,63%</t>
+          <t>79,84%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5004,32 +5004,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>1294681</t>
+          <t>1226500</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1217389</t>
+          <t>1188717</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>1424586</t>
+          <t>1260087</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>78,63%</t>
+          <t>75,27%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>73,94%</t>
+          <t>72,95%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>86,52%</t>
+          <t>77,33%</t>
         </is>
       </c>
     </row>
@@ -5047,32 +5047,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>96019</t>
+          <t>110530</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>40705</t>
+          <t>92579</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>138838</t>
+          <t>132129</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5082,32 +5082,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>92698</t>
+          <t>101461</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>76761</t>
+          <t>86062</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>112167</t>
+          <t>120843</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5117,32 +5117,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>188717</t>
+          <t>211991</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>120564</t>
+          <t>185773</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>234025</t>
+          <t>237331</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,57%</t>
         </is>
       </c>
     </row>
@@ -5160,17 +5160,17 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5195,17 +5195,17 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5230,17 +5230,17 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5277,32 +5277,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>204371</t>
+          <t>210241</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>158122</t>
+          <t>179966</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>247224</t>
+          <t>245850</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5312,32 +5312,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>386008</t>
+          <t>201038</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>181595</t>
+          <t>176869</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>1118414</t>
+          <t>230049</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5347,32 +5347,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>590379</t>
+          <t>411279</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>379476</t>
+          <t>370773</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>1380234</t>
+          <t>459581</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>6,33%</t>
         </is>
       </c>
     </row>
@@ -5390,32 +5390,32 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>608570</t>
+          <t>637646</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>467138</t>
+          <t>587398</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>674007</t>
+          <t>691396</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5425,32 +5425,32 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>530565</t>
+          <t>573844</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>435251</t>
+          <t>536409</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>583919</t>
+          <t>621771</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5460,32 +5460,32 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>1139135</t>
+          <t>1211491</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>974631</t>
+          <t>1150027</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>1244859</t>
+          <t>1281819</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,65%</t>
         </is>
       </c>
     </row>
@@ -5503,32 +5503,32 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>2021844</t>
+          <t>1954952</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>1894690</t>
+          <t>1895314</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>2369611</t>
+          <t>2032830</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>58,46%</t>
+          <t>55,37%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>54,78%</t>
+          <t>53,68%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>68,51%</t>
+          <t>57,58%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5538,32 +5538,32 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>2020963</t>
+          <t>2184519</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>1615310</t>
+          <t>2127672</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>2174129</t>
+          <t>2236697</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>55,24%</t>
+          <t>58,54%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>44,15%</t>
+          <t>57,02%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>59,42%</t>
+          <t>59,94%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5573,32 +5573,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>4042807</t>
+          <t>4139471</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>3688216</t>
+          <t>4048611</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>4347843</t>
+          <t>4219216</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>56,8%</t>
+          <t>57,0%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>51,82%</t>
+          <t>55,75%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>61,09%</t>
+          <t>58,1%</t>
         </is>
       </c>
     </row>
@@ -5616,32 +5616,32 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>623839</t>
+          <t>727723</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>489481</t>
+          <t>675106</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>694271</t>
+          <t>781812</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5651,32 +5651,32 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>721136</t>
+          <t>772276</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>607721</t>
+          <t>730472</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>812179</t>
+          <t>815131</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5686,32 +5686,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>1344975</t>
+          <t>1499999</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>1157964</t>
+          <t>1434999</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>1480467</t>
+          <t>1574613</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>21,68%</t>
         </is>
       </c>
     </row>
@@ -5729,17 +5729,17 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>3458624</t>
+          <t>3530562</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>3458624</t>
+          <t>3530562</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>3458624</t>
+          <t>3530562</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5764,17 +5764,17 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>3658672</t>
+          <t>3731678</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>3658672</t>
+          <t>3731678</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>3658672</t>
+          <t>3731678</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5799,17 +5799,17 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>7117296</t>
+          <t>7262240</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>7117296</t>
+          <t>7262240</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>7117296</t>
+          <t>7262240</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
